--- a/artfynd/A 40214-2026 artfynd.xlsx
+++ b/artfynd/A 40214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137522976</v>
       </c>
       <c r="B2" t="n">
-        <v>79357</v>
+        <v>79360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137522877</v>
       </c>
       <c r="B3" t="n">
-        <v>96343</v>
+        <v>96346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>137522815</v>
       </c>
       <c r="B4" t="n">
-        <v>96660</v>
+        <v>96663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>137522829</v>
       </c>
       <c r="B5" t="n">
-        <v>96660</v>
+        <v>96663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>137522998</v>
       </c>
       <c r="B6" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
